--- a/weights/per_results.xlsx
+++ b/weights/per_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,607 +417,607 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Avg_0.4</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Std_0.4</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Min_0.4</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Max_0.4</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Avg_0.45</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Std_0.45</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Min_0.45</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_0.45</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Avg_0.5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Std_0.5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Min_0.5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Max_0.5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Avg_0.54</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Std_0.54</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Min_0.54</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Max_0.54</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Avg_0.59</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Std_0.59</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Min_0.59</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Max_0.59</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Avg_0.64</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Std_0.64</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Min_0.64</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Max_0.64</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Avg_0.69</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Std_0.69</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Min_0.69</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Max_0.69</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Avg_0.74</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Std_0.74</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Min_0.74</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Max_0.74</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Avg_0.79</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Std_0.79</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Min_0.79</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Max_0.79</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Avg_0.83</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Std_0.83</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Min_0.83</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Max_0.83</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Avg_0.88</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Std_0.88</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Min_0.88</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Max_0.88</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Avg_0.93</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Std_0.93</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Min_0.93</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Max_0.93</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Avg_0.98</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Std_0.98</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Min_0.98</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Max_0.98</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Avg_1.03</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Std_1.03</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Min_1.03</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Max_1.03</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Avg_1.08</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Std_1.08</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Min_1.08</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Max_1.08</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Avg_1.12</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Std_1.12</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Min_1.12</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Max_1.12</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Avg_1.17</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Std_1.17</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Min_1.17</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Max_1.17</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Avg_1.22</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Std_1.22</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Min_1.22</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Max_1.22</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Avg_1.27</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Std_1.27</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Min_1.27</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Max_1.27</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Avg_1.32</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Std_1.32</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>Min_1.32</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>Max_1.32</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>Avg_1.37</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>Std_1.37</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>Min_1.37</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>Max_1.37</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>Avg_1.41</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>Std_1.41</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>Min_1.41</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>Max_1.41</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>Avg_1.46</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>Std_1.46</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>Min_1.46</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>Max_1.46</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>Avg_1.51</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>Std_1.51</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>Min_1.51</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>Max_1.51</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>Avg_1.56</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>Std_1.56</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>Min_1.56</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>Max_1.56</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>Avg_1.61</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>Std_1.61</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>Min_1.61</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>Max_1.61</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>Avg_1.66</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>Std_1.66</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>Min_1.66</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>Max_1.66</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>Avg_1.7</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>Std_1.7</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>Min_1.7</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>Max_1.7</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>Avg_1.75</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>Std_1.75</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>Min_1.75</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>Max_1.75</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>Avg_1.8</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>Std_1.8</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>Min_1.8</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>Max_1.8</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>Total_Avg</t>
         </is>
@@ -1037,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>991.9</v>
+        <v>342.6</v>
       </c>
       <c r="B2" t="n">
-        <v>453.3847041972193</v>
+        <v>204.3091774737493</v>
       </c>
       <c r="C2" t="n">
-        <v>513</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n">
-        <v>1723</v>
+        <v>522</v>
       </c>
       <c r="E2" t="n">
-        <v>1103.4</v>
+        <v>466.3</v>
       </c>
       <c r="F2" t="n">
-        <v>770.8874366598537</v>
+        <v>125.4663699961069</v>
       </c>
       <c r="G2" t="n">
-        <v>505</v>
+        <v>91</v>
       </c>
       <c r="H2" t="n">
-        <v>3121</v>
+        <v>536</v>
       </c>
       <c r="I2" t="n">
-        <v>1026.6</v>
+        <v>431.3</v>
       </c>
       <c r="J2" t="n">
-        <v>697.5865824397714</v>
+        <v>168.7572516960383</v>
       </c>
       <c r="K2" t="n">
+        <v>89</v>
+      </c>
+      <c r="L2" t="n">
+        <v>546</v>
+      </c>
+      <c r="M2" t="n">
+        <v>510.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.362744053679987</v>
+      </c>
+      <c r="O2" t="n">
         <v>503</v>
       </c>
-      <c r="L2" t="n">
-        <v>2313</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1232.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>907.4894214259471</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
+        <v>526</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>516.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>31.9720190166339</v>
+      </c>
+      <c r="S2" t="n">
+        <v>503</v>
+      </c>
+      <c r="T2" t="n">
+        <v>612</v>
+      </c>
+      <c r="U2" t="n">
+        <v>506.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6.15223536610881</v>
+      </c>
+      <c r="W2" t="n">
+        <v>503</v>
+      </c>
+      <c r="X2" t="n">
+        <v>524</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>588.6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>80.92737484930547</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>503</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>763</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>456.5869139605296</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>504</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2047</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>565.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>55.79462339688296</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>504</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>679</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>547.6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>34.98056603315618</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>504</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>590</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>951.7</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1086.593488844839</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>511</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4192</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1795.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1979.392421931538</v>
+      </c>
+      <c r="AU2" t="n">
         <v>506</v>
       </c>
-      <c r="P2" t="n">
-        <v>2707</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>732</v>
-      </c>
-      <c r="R2" t="n">
-        <v>435.9827978257858</v>
-      </c>
-      <c r="S2" t="n">
-        <v>512</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="U2" t="n">
-        <v>550.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>40.80502420045845</v>
-      </c>
-      <c r="W2" t="n">
-        <v>509</v>
-      </c>
-      <c r="X2" t="n">
-        <v>653</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>547.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>52.21886632243178</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>508</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>650</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>530.9</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15.25417975507041</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>507</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>558</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>588.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>67.29524500289749</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>507</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>672</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>580.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>134.6441606606094</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>503</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>961</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1497.9</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1467.317174301453</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>506</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4549</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>688.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>165.2439408874044</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>509</v>
-      </c>
       <c r="AV2" t="n">
-        <v>1009</v>
+        <v>5571</v>
       </c>
       <c r="AW2" t="n">
-        <v>614.3</v>
+        <v>945.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>141.3605673446453</v>
+        <v>1170.733001157822</v>
       </c>
       <c r="AY2" t="n">
         <v>509</v>
       </c>
       <c r="AZ2" t="n">
-        <v>904</v>
+        <v>4457</v>
       </c>
       <c r="BA2" t="n">
-        <v>1130.7</v>
+        <v>1312.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1137.866868311052</v>
+        <v>1605.956366156939</v>
       </c>
       <c r="BC2" t="n">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="BD2" t="n">
-        <v>4459</v>
+        <v>5549</v>
       </c>
       <c r="BE2" t="n">
-        <v>773</v>
+        <v>2077.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>197.9085647464505</v>
+        <v>2338.108945280352</v>
       </c>
       <c r="BG2" t="n">
+        <v>519</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>6131</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>576.3</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>54.82161982283996</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>503</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>668</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2028.7</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1876.893233511166</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>514</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>5096</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1476.2</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1407.57769234952</v>
+      </c>
+      <c r="BS2" t="n">
         <v>504</v>
       </c>
-      <c r="BH2" t="n">
-        <v>1196</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>740.9</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>206.7798104264534</v>
-      </c>
-      <c r="BK2" t="n">
+      <c r="BT2" t="n">
+        <v>3748</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>599.2</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>132.497396200831</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>504</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>865</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>561.6</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>45.26853211669228</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>513</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>670</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>551.6</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>40.8391968579207</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>510</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>646</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>556.1</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>166.0623075836296</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>120</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>781</v>
+      </c>
+      <c r="CK2" t="n">
         <v>532</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1209</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>956.4</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>947.03983020779</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>230</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>3718</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1334.1</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1383.211585405501</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>276</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>4081</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>886.8</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1036.719614939353</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>283</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>3927</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>978</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1485.782352836377</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>218</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>5393</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>533.7</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>239.9100039598182</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>201</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>897</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>322</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>90.8493258092761</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>187</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>514</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>421.1</v>
-      </c>
       <c r="CL2" t="n">
-        <v>169.5821040086483</v>
+        <v>143.326899080389</v>
       </c>
       <c r="CM2" t="n">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="CN2" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="CO2" t="n">
-        <v>566.7</v>
+        <v>489.7</v>
       </c>
       <c r="CP2" t="n">
-        <v>749.055812339775</v>
+        <v>139.9321621358007</v>
       </c>
       <c r="CQ2" t="n">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="CR2" t="n">
-        <v>2791</v>
+        <v>621</v>
       </c>
       <c r="CS2" t="n">
-        <v>317.3</v>
+        <v>674</v>
       </c>
       <c r="CT2" t="n">
-        <v>97.40641662642147</v>
+        <v>616.4462669203212</v>
       </c>
       <c r="CU2" t="n">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="CV2" t="n">
-        <v>494</v>
+        <v>2444</v>
       </c>
       <c r="CW2" t="n">
-        <v>230.6</v>
+        <v>318.8</v>
       </c>
       <c r="CX2" t="n">
-        <v>54.54942712806433</v>
+        <v>185.8207738655719</v>
       </c>
       <c r="CY2" t="n">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="CZ2" t="n">
-        <v>338</v>
+        <v>591</v>
       </c>
       <c r="DA2" t="n">
-        <v>291.9</v>
+        <v>243.7</v>
       </c>
       <c r="DB2" t="n">
-        <v>105.7472931095638</v>
+        <v>189.7387941355167</v>
       </c>
       <c r="DC2" t="n">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="DD2" t="n">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="DE2" t="n">
-        <v>316</v>
+        <v>149.6</v>
       </c>
       <c r="DF2" t="n">
-        <v>95.16511966051426</v>
+        <v>38.29673615335907</v>
       </c>
       <c r="DG2" t="n">
-        <v>202</v>
+        <v>86</v>
       </c>
       <c r="DH2" t="n">
-        <v>492</v>
+        <v>210</v>
       </c>
       <c r="DI2" t="n">
-        <v>348.7</v>
+        <v>379.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>272.4078009161999</v>
+        <v>212.5946612688099</v>
       </c>
       <c r="DK2" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="DL2" t="n">
-        <v>1149</v>
+        <v>581</v>
       </c>
       <c r="DM2" t="n">
-        <v>223.1</v>
+        <v>387</v>
       </c>
       <c r="DN2" t="n">
-        <v>31.02079947390138</v>
+        <v>208.9966506908663</v>
       </c>
       <c r="DO2" t="n">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="DP2" t="n">
-        <v>288</v>
+        <v>616</v>
       </c>
       <c r="DQ2" t="n">
-        <v>21055.9</v>
+        <v>21762.19999999999</v>
       </c>
     </row>
   </sheetData>

--- a/weights/per_results.xlsx
+++ b/weights/per_results.xlsx
@@ -1025,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>342.6</v>
+        <v>113.4</v>
       </c>
       <c r="B2" t="n">
-        <v>204.3091774737493</v>
+        <v>2.690724809414742</v>
       </c>
       <c r="C2" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>522</v>
+        <v>118</v>
       </c>
       <c r="E2" t="n">
-        <v>466.3</v>
+        <v>113.2</v>
       </c>
       <c r="F2" t="n">
-        <v>125.4663699961069</v>
+        <v>3.919183588453084</v>
       </c>
       <c r="G2" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="H2" t="n">
-        <v>536</v>
+        <v>121</v>
       </c>
       <c r="I2" t="n">
-        <v>431.3</v>
+        <v>116.5</v>
       </c>
       <c r="J2" t="n">
-        <v>168.7572516960383</v>
+        <v>2.459674775249769</v>
       </c>
       <c r="K2" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="L2" t="n">
-        <v>546</v>
+        <v>121</v>
       </c>
       <c r="M2" t="n">
-        <v>510.7</v>
+        <v>115.8</v>
       </c>
       <c r="N2" t="n">
-        <v>7.362744053679987</v>
+        <v>1.98997487421324</v>
       </c>
       <c r="O2" t="n">
-        <v>503</v>
+        <v>111</v>
       </c>
       <c r="P2" t="n">
-        <v>526</v>
+        <v>118</v>
       </c>
       <c r="Q2" t="n">
-        <v>516.3</v>
+        <v>116.6</v>
       </c>
       <c r="R2" t="n">
-        <v>31.9720190166339</v>
+        <v>2.289104628451919</v>
       </c>
       <c r="S2" t="n">
-        <v>503</v>
+        <v>114</v>
       </c>
       <c r="T2" t="n">
-        <v>612</v>
+        <v>121</v>
       </c>
       <c r="U2" t="n">
-        <v>506.5</v>
+        <v>117.4</v>
       </c>
       <c r="V2" t="n">
-        <v>6.15223536610881</v>
+        <v>1.562049935181331</v>
       </c>
       <c r="W2" t="n">
-        <v>503</v>
+        <v>115</v>
       </c>
       <c r="X2" t="n">
-        <v>524</v>
+        <v>121</v>
       </c>
       <c r="Y2" t="n">
-        <v>588.6</v>
+        <v>119.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>80.92737484930547</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>503</v>
+        <v>116</v>
       </c>
       <c r="AB2" t="n">
-        <v>763</v>
+        <v>123</v>
       </c>
       <c r="AC2" t="n">
-        <v>680.7</v>
+        <v>119.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>456.5869139605296</v>
+        <v>1.562049935181331</v>
       </c>
       <c r="AE2" t="n">
-        <v>504</v>
+        <v>117</v>
       </c>
       <c r="AF2" t="n">
-        <v>2047</v>
+        <v>123</v>
       </c>
       <c r="AG2" t="n">
-        <v>565.4</v>
+        <v>115.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>55.79462339688296</v>
+        <v>2.939387691339814</v>
       </c>
       <c r="AI2" t="n">
-        <v>504</v>
+        <v>111</v>
       </c>
       <c r="AJ2" t="n">
-        <v>679</v>
+        <v>122</v>
       </c>
       <c r="AK2" t="n">
-        <v>547.6</v>
+        <v>118.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>34.98056603315618</v>
+        <v>2.90516780926679</v>
       </c>
       <c r="AM2" t="n">
-        <v>504</v>
+        <v>114</v>
       </c>
       <c r="AN2" t="n">
-        <v>590</v>
+        <v>123</v>
       </c>
       <c r="AO2" t="n">
-        <v>951.7</v>
+        <v>118</v>
       </c>
       <c r="AP2" t="n">
-        <v>1086.593488844839</v>
+        <v>2.792848008753788</v>
       </c>
       <c r="AQ2" t="n">
-        <v>511</v>
+        <v>114</v>
       </c>
       <c r="AR2" t="n">
-        <v>4192</v>
+        <v>122</v>
       </c>
       <c r="AS2" t="n">
-        <v>1795.2</v>
+        <v>122.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1979.392421931538</v>
+        <v>4.72122865364515</v>
       </c>
       <c r="AU2" t="n">
-        <v>506</v>
+        <v>116</v>
       </c>
       <c r="AV2" t="n">
-        <v>5571</v>
+        <v>131</v>
       </c>
       <c r="AW2" t="n">
-        <v>945.8</v>
+        <v>123.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>1170.733001157822</v>
+        <v>4.134005321718877</v>
       </c>
       <c r="AY2" t="n">
-        <v>509</v>
+        <v>118</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4457</v>
+        <v>130</v>
       </c>
       <c r="BA2" t="n">
-        <v>1312.5</v>
+        <v>125</v>
       </c>
       <c r="BB2" t="n">
-        <v>1605.956366156939</v>
+        <v>6.434283176858165</v>
       </c>
       <c r="BC2" t="n">
-        <v>503</v>
+        <v>116</v>
       </c>
       <c r="BD2" t="n">
-        <v>5549</v>
+        <v>135</v>
       </c>
       <c r="BE2" t="n">
-        <v>2077.4</v>
+        <v>133.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>2338.108945280352</v>
+        <v>4.920365840057017</v>
       </c>
       <c r="BG2" t="n">
-        <v>519</v>
+        <v>124</v>
       </c>
       <c r="BH2" t="n">
-        <v>6131</v>
+        <v>144</v>
       </c>
       <c r="BI2" t="n">
-        <v>576.3</v>
+        <v>136.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>54.82161982283996</v>
+        <v>4.548626166217663</v>
       </c>
       <c r="BK2" t="n">
-        <v>503</v>
+        <v>130</v>
       </c>
       <c r="BL2" t="n">
-        <v>668</v>
+        <v>145</v>
       </c>
       <c r="BM2" t="n">
-        <v>2028.7</v>
+        <v>128.3</v>
       </c>
       <c r="BN2" t="n">
-        <v>1876.893233511166</v>
+        <v>16.21141573089778</v>
       </c>
       <c r="BO2" t="n">
-        <v>514</v>
+        <v>85</v>
       </c>
       <c r="BP2" t="n">
-        <v>5096</v>
+        <v>142</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1476.2</v>
+        <v>122.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>1407.57769234952</v>
+        <v>8.534635317340747</v>
       </c>
       <c r="BS2" t="n">
-        <v>504</v>
+        <v>110</v>
       </c>
       <c r="BT2" t="n">
-        <v>3748</v>
+        <v>138</v>
       </c>
       <c r="BU2" t="n">
-        <v>599.2</v>
+        <v>121.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>132.497396200831</v>
+        <v>9.00222194794152</v>
       </c>
       <c r="BW2" t="n">
-        <v>504</v>
+        <v>108</v>
       </c>
       <c r="BX2" t="n">
-        <v>865</v>
+        <v>140</v>
       </c>
       <c r="BY2" t="n">
-        <v>561.6</v>
+        <v>120.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>45.26853211669228</v>
+        <v>3.969886648255841</v>
       </c>
       <c r="CA2" t="n">
-        <v>513</v>
+        <v>115</v>
       </c>
       <c r="CB2" t="n">
-        <v>670</v>
+        <v>127</v>
       </c>
       <c r="CC2" t="n">
-        <v>551.6</v>
+        <v>123.2</v>
       </c>
       <c r="CD2" t="n">
-        <v>40.8391968579207</v>
+        <v>3.815756805667782</v>
       </c>
       <c r="CE2" t="n">
-        <v>510</v>
+        <v>117</v>
       </c>
       <c r="CF2" t="n">
-        <v>646</v>
+        <v>130</v>
       </c>
       <c r="CG2" t="n">
-        <v>556.1</v>
+        <v>121.5</v>
       </c>
       <c r="CH2" t="n">
-        <v>166.0623075836296</v>
+        <v>2.872281323269014</v>
       </c>
       <c r="CI2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="CJ2" t="n">
-        <v>781</v>
+        <v>129</v>
       </c>
       <c r="CK2" t="n">
-        <v>532</v>
+        <v>123.2</v>
       </c>
       <c r="CL2" t="n">
-        <v>143.326899080389</v>
+        <v>3.42928563989645</v>
       </c>
       <c r="CM2" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="CN2" t="n">
-        <v>699</v>
+        <v>128</v>
       </c>
       <c r="CO2" t="n">
-        <v>489.7</v>
+        <v>102.9</v>
       </c>
       <c r="CP2" t="n">
-        <v>139.9321621358007</v>
+        <v>39.90100249367176</v>
       </c>
       <c r="CQ2" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="CR2" t="n">
-        <v>621</v>
+        <v>130</v>
       </c>
       <c r="CS2" t="n">
-        <v>674</v>
+        <v>121.2</v>
       </c>
       <c r="CT2" t="n">
-        <v>616.4462669203212</v>
+        <v>7.520638270785266</v>
       </c>
       <c r="CU2" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="CV2" t="n">
-        <v>2444</v>
+        <v>129</v>
       </c>
       <c r="CW2" t="n">
-        <v>318.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="CX2" t="n">
-        <v>185.8207738655719</v>
+        <v>45.47405853890765</v>
       </c>
       <c r="CY2" t="n">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="CZ2" t="n">
-        <v>591</v>
+        <v>132</v>
       </c>
       <c r="DA2" t="n">
-        <v>243.7</v>
+        <v>100.7</v>
       </c>
       <c r="DB2" t="n">
-        <v>189.7387941355167</v>
+        <v>38.64983829202912</v>
       </c>
       <c r="DC2" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="DD2" t="n">
-        <v>550</v>
+        <v>123</v>
       </c>
       <c r="DE2" t="n">
-        <v>149.6</v>
+        <v>109.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>38.29673615335907</v>
+        <v>29.02223285689783</v>
       </c>
       <c r="DG2" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="DH2" t="n">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="DI2" t="n">
-        <v>379.1</v>
+        <v>109.2</v>
       </c>
       <c r="DJ2" t="n">
-        <v>212.5946612688099</v>
+        <v>28.7986110776197</v>
       </c>
       <c r="DK2" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="DL2" t="n">
-        <v>581</v>
+        <v>122</v>
       </c>
       <c r="DM2" t="n">
-        <v>387</v>
+        <v>120.9</v>
       </c>
       <c r="DN2" t="n">
-        <v>208.9966506908663</v>
+        <v>5.204805471869242</v>
       </c>
       <c r="DO2" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="DP2" t="n">
-        <v>616</v>
+        <v>127</v>
       </c>
       <c r="DQ2" t="n">
-        <v>21762.19999999999</v>
+        <v>3543.9</v>
       </c>
     </row>
   </sheetData>

--- a/weights/per_results.xlsx
+++ b/weights/per_results.xlsx
@@ -1025,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113.4</v>
+        <v>94.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.690724809414742</v>
+        <v>3.42928563989645</v>
       </c>
       <c r="C2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E2" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.33238075793812</v>
+      </c>
+      <c r="G2" t="n">
+        <v>92</v>
+      </c>
+      <c r="H2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I2" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>89</v>
+      </c>
+      <c r="L2" t="n">
+        <v>101</v>
+      </c>
+      <c r="M2" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.467792535850613</v>
+      </c>
+      <c r="O2" t="n">
+        <v>92</v>
+      </c>
+      <c r="P2" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.317406628984581</v>
+      </c>
+      <c r="S2" t="n">
+        <v>87</v>
+      </c>
+      <c r="T2" t="n">
+        <v>101</v>
+      </c>
+      <c r="U2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.618010503025109</v>
+      </c>
+      <c r="W2" t="n">
+        <v>88</v>
+      </c>
+      <c r="X2" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.838388161361178</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.370459909270544</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4.477722635447623</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>84</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4.605431575867782</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.360059523282289</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>92</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.242640687119285</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.870540018881464</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.805205510693585</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>83</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>96</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.91024295920343</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>89</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>102</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2.451530134426252</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>93</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.526588119102509</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>87</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>3.693237062523877</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>3.238826948140329</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>89</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.891366458960193</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>96</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>105</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>3.63868107973205</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>93</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>105</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>2.343074902771996</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>93</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>3.014962686336267</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>95</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>106</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>4.521061822182926</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>92</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>106</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>4.386342439892261</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>97</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>109</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>4.476605857119878</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>97</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>109</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>3.42928563989645</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>95</v>
+      </c>
+      <c r="DD2" t="n">
         <v>108</v>
       </c>
-      <c r="D2" t="n">
-        <v>118</v>
-      </c>
-      <c r="E2" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.919183588453084</v>
-      </c>
-      <c r="G2" t="n">
-        <v>106</v>
-      </c>
-      <c r="H2" t="n">
-        <v>121</v>
-      </c>
-      <c r="I2" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.459674775249769</v>
-      </c>
-      <c r="K2" t="n">
-        <v>113</v>
-      </c>
-      <c r="L2" t="n">
-        <v>121</v>
-      </c>
-      <c r="M2" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.98997487421324</v>
-      </c>
-      <c r="O2" t="n">
-        <v>111</v>
-      </c>
-      <c r="P2" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>116.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.289104628451919</v>
-      </c>
-      <c r="S2" t="n">
-        <v>114</v>
-      </c>
-      <c r="T2" t="n">
-        <v>121</v>
-      </c>
-      <c r="U2" t="n">
-        <v>117.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.562049935181331</v>
-      </c>
-      <c r="W2" t="n">
-        <v>115</v>
-      </c>
-      <c r="X2" t="n">
-        <v>121</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>119.1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>116</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>123</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>119.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.562049935181331</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>117</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>123</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.939387691339814</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>111</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>122</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>118.6</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.90516780926679</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>123</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>118</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.792848008753788</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>114</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>122</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>122.9</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.72122865364515</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>116</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>131</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.134005321718877</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>118</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>130</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>125</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.434283176858165</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>116</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>135</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>133.7</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.920365840057017</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>124</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>144</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>136.9</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>4.548626166217663</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>130</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>145</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>128.3</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>16.21141573089778</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>142</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>122.6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>8.534635317340747</v>
-      </c>
-      <c r="BS2" t="n">
+      <c r="DE2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>4.220189569201838</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>96</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>108</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>5.281098370604357</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>92</v>
+      </c>
+      <c r="DL2" t="n">
         <v>110</v>
       </c>
-      <c r="BT2" t="n">
-        <v>138</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>9.00222194794152</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>108</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>3.969886648255841</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>115</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>127</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>123.2</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>3.815756805667782</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>117</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>130</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>2.872281323269014</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>118</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>129</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>123.2</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>3.42928563989645</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>118</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>128</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>39.90100249367176</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>23</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>130</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>121.2</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>7.520638270785266</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>101</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>129</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>45.47405853890765</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>22</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>132</v>
-      </c>
-      <c r="DA2" t="n">
+      <c r="DM2" t="n">
         <v>100.7</v>
       </c>
-      <c r="DB2" t="n">
-        <v>38.64983829202912</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>123</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>109.1</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>29.02223285689783</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>25</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>127</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>109.2</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>28.7986110776197</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>23</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>122</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>120.9</v>
-      </c>
       <c r="DN2" t="n">
-        <v>5.204805471869242</v>
+        <v>3.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="DP2" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="DQ2" t="n">
-        <v>3543.9</v>
+        <v>2900.2</v>
       </c>
     </row>
   </sheetData>
